--- a/output/stock_quant_scores/ASML_balance_df.xlsx
+++ b/output/stock_quant_scores/ASML_balance_df.xlsx
@@ -1821,23 +1821,33 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>4584100000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>5892200000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>10140600000</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>8317300000</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>20090400000</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1845,7 +1855,9 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>12298000000</v>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1855,7 +1867,9 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>30231000000</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
@@ -1880,11 +1894,15 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>18190200000</v>
+      </c>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>5179200000</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
@@ -1897,7 +1915,9 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
+      <c r="CA6" t="n">
+        <v>6951800000</v>
+      </c>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
     </row>
